--- a/data-manipulation-scripts/sheets-cleanup/sheets/BOMBA FREIO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/BOMBA FREIO.xlsx
@@ -122,7 +122,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -395,7 +395,9 @@
       <c r="C2" s="4">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>80.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -465,7 +467,9 @@
       <c r="C4" s="4">
         <v>1.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5">
+        <v>70.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -499,7 +503,9 @@
       <c r="C5" s="7">
         <v>1.0</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="5">
+        <v>113.0</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
